--- a/cv.xlsx
+++ b/cv.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="163" uniqueCount="116">
   <si>
     <t xml:space="preserve">date_start</t>
   </si>
@@ -123,7 +123,7 @@
     <t xml:space="preserve">Research Assistant</t>
   </si>
   <si>
-    <t xml:space="preserve">During this time I had several part time contracts with several institutions as part time and substitute staff. Duties and responsibilities included research assistance, marking, creating lecure notes, lab assistance etc.</t>
+    <t xml:space="preserve">During this time I had several part time contracts with several institutions as part time and substitute staff. Duties and responsibilities included research assistance, marking, creating lecture notes, lab assistance etc.</t>
   </si>
   <si>
     <t xml:space="preserve">institution</t>
@@ -204,7 +204,7 @@
     <t xml:space="preserve">Item Response Theory</t>
   </si>
   <si>
-    <t xml:space="preserve">https://dimitrios.shinyapps.io/modelsirt/</t>
+    <t xml:space="preserve">https://sedzinfo.github.io/vignettes/cat_irt_eap/</t>
   </si>
   <si>
     <t xml:space="preserve">TIRT</t>
@@ -279,18 +279,36 @@
     <t xml:space="preserve">Interactive Data Visualization</t>
   </si>
   <si>
-    <t xml:space="preserve">https://dimitrios.shinyapps.io/worldbank/</t>
+    <t xml:space="preserve">https://sedzinfo.shinyapps.io/golemworldbank/</t>
   </si>
   <si>
     <t xml:space="preserve">shiny</t>
   </si>
   <si>
+    <t xml:space="preserve">https://sedzinfo-golemcrypto.share.connect.posit.cloud/</t>
+  </si>
+  <si>
+    <t xml:space="preserve">golem</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sedzinfo-golemirt.share.connect.posit.cloud/</t>
+  </si>
+  <si>
     <t xml:space="preserve">grafana</t>
   </si>
   <si>
     <t xml:space="preserve">https://sedzinfo.grafana.net/public-dashboards/425b920caf1b48dfb15fc829d322e949</t>
   </si>
   <si>
+    <t xml:space="preserve">Documentation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pkgdown</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://sedzinfo.github.io/rwf/</t>
+  </si>
+  <si>
     <t xml:space="preserve">icon</t>
   </si>
   <si>
@@ -343,15 +361,6 @@
   </si>
   <si>
     <t xml:space="preserve">https://github.com/sedzinfo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">\faGlobe\</t>
-  </si>
-  <si>
-    <t xml:space="preserve">rpubs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://rpubs.com/sedzinfo</t>
   </si>
   <si>
     <t xml:space="preserve">\faMapMarker\</t>
@@ -457,12 +466,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="20" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1050,7 +1055,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D16"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="18.57"/>
@@ -1073,7 +1078,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
         <v>44</v>
       </c>
@@ -1087,7 +1092,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
         <v>44</v>
       </c>
@@ -1101,7 +1106,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
         <v>44</v>
       </c>
@@ -1115,7 +1120,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
         <v>44</v>
       </c>
@@ -1129,7 +1134,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
         <v>44</v>
       </c>
@@ -1143,7 +1148,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
         <v>44</v>
       </c>
@@ -1157,7 +1162,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="s">
         <v>44</v>
       </c>
@@ -1171,7 +1176,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="s">
         <v>44</v>
       </c>
@@ -1185,7 +1190,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="s">
         <v>44</v>
       </c>
@@ -1199,7 +1204,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="s">
         <v>44</v>
       </c>
@@ -1213,7 +1218,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="0" t="s">
         <v>44</v>
       </c>
@@ -1227,7 +1232,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="13" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="0" t="s">
         <v>78</v>
       </c>
@@ -1241,7 +1246,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="0" t="s">
         <v>78</v>
       </c>
@@ -1255,7 +1260,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="0" t="s">
         <v>78</v>
       </c>
@@ -1266,41 +1271,53 @@
         <v>85</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="16.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="0" t="s">
         <v>78</v>
       </c>
       <c r="B16" s="0" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C16" s="0" t="s">
-        <v>86</v>
-      </c>
-      <c r="D16" s="1" t="s">
         <v>87</v>
       </c>
-    </row>
+      <c r="D16" s="0" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="0" t="s">
+        <v>78</v>
+      </c>
+      <c r="B17" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="C17" s="0" t="s">
+        <v>89</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="0" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="C18" s="0" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="0" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" display="https://rpubs.com/sedzinfo/glm_anova"/>
-    <hyperlink ref="D3" r:id="rId2" display="https://rpubs.com/sedzinfo/generalized_linear_models"/>
-    <hyperlink ref="D4" r:id="rId3" display="https://rpubs.com/sedzinfo/cfa_mi"/>
-    <hyperlink ref="D5" r:id="rId4" display="https://rpubs.com/sedzinfo/glm_efa"/>
-    <hyperlink ref="D6" r:id="rId5" display="https://dimitrios.shinyapps.io/modelsirt/"/>
-    <hyperlink ref="D7" r:id="rId6" display="https://rpubs.com/sedzinfo/tirt"/>
-    <hyperlink ref="D8" r:id="rId7" display="https://rpubs.com/sedzinfo/functions_train_test"/>
-    <hyperlink ref="D9" r:id="rId8" display="https://rpubs.com/sedzinfo/nlp"/>
-    <hyperlink ref="D10" r:id="rId9" display="https://rpubs.com/sedzinfo/keras_mnist"/>
-    <hyperlink ref="D11" r:id="rId10" display="https://rpubs.com/sedzinfo/lda"/>
-    <hyperlink ref="D12" r:id="rId11" display="https://rpubs.com/sedzinfo/rpart"/>
-    <hyperlink ref="D13" r:id="rId12" display="https://github.com/sedzinfo/snp"/>
-    <hyperlink ref="D14" r:id="rId13" display="https://dimitrios.shinyapps.io/worldbank/"/>
-    <hyperlink ref="D15" r:id="rId14" display="https://dimitrios.shinyapps.io/worldbank/"/>
-    <hyperlink ref="D16" r:id="rId15" display="https://sedzinfo.grafana.net/public-dashboards/425b920caf1b48dfb15fc829d322e949"/>
-  </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
@@ -1334,7 +1351,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D8"/>
+  <dimension ref="A1:D1048576"/>
   <sheetFormatPr defaultColWidth="8.57421875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="14.29"/>
@@ -1343,116 +1360,103 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B1" s="0" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="C1" s="0" t="s">
         <v>43</v>
       </c>
       <c r="D1" s="0" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="B2" s="0" t="s">
-        <v>92</v>
-      </c>
-      <c r="C2" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>92</v>
+        <v>98</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="s">
-        <v>94</v>
+        <v>100</v>
       </c>
       <c r="B3" s="0" t="s">
-        <v>95</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="D3" s="2" t="n">
+        <v>101</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>102</v>
+      </c>
+      <c r="D3" s="1" t="n">
         <v>6947863817</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="s">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="B4" s="0" t="s">
-        <v>98</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="s">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="B5" s="0" t="s">
-        <v>101</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>101</v>
+        <v>107</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="0" t="s">
-        <v>103</v>
+        <v>109</v>
       </c>
       <c r="B6" s="0" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
       <c r="C6" s="0" t="s">
-        <v>105</v>
+        <v>111</v>
       </c>
       <c r="D6" s="0" t="s">
-        <v>104</v>
+        <v>110</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
       <c r="B7" s="0" t="s">
-        <v>107</v>
+        <v>5</v>
       </c>
       <c r="C7" s="0" t="s">
-        <v>108</v>
+        <v>113</v>
       </c>
       <c r="D7" s="0" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="0" t="s">
-        <v>109</v>
-      </c>
-      <c r="B8" s="0" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="0" t="s">
-        <v>110</v>
-      </c>
-      <c r="D8" s="0" t="s">
-        <v>110</v>
-      </c>
-    </row>
+        <v>113</v>
+      </c>
+    </row>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
@@ -1477,12 +1481,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="0" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
-        <v>112</v>
+      <c r="A2" s="3" t="s">
+        <v>115</v>
       </c>
     </row>
   </sheetData>
